--- a/code/curvature_results.xlsx
+++ b/code/curvature_results.xlsx
@@ -622,100 +622,100 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.777096502388321</v>
+        <v>3.908539868790847</v>
       </c>
       <c r="C2" t="n">
-        <v>1.02339250202387</v>
+        <v>1.095301941336491</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8751958343165136</v>
+        <v>0.8814517231782427</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7989031788207143</v>
+        <v>0.8008271393317827</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7338398044477625</v>
+        <v>0.7452370352948111</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6716586874691273</v>
+        <v>0.6896494413021956</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6132090683754844</v>
+        <v>0.6315588609032777</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5601874600676187</v>
+        <v>0.5733352435583239</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5135573377530718</v>
+        <v>0.5174755779248672</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4735348523737284</v>
+        <v>0.4656475689070874</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4398399170268089</v>
+        <v>0.4187173425838436</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4119226035044996</v>
+        <v>0.3769693432759335</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3891195000654271</v>
+        <v>0.3403137479269897</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3707497574156333</v>
+        <v>0.3084416138771426</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3561686542252529</v>
+        <v>0.280930997209608</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3447937495672887</v>
+        <v>0.25731576263815</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3361143785294786</v>
+        <v>0.2371281313320854</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3296916245578286</v>
+        <v>0.2199234791037117</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3251532872276562</v>
+        <v>0.2052934796057553</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3221865983389419</v>
+        <v>0.1928718029743673</v>
       </c>
       <c r="V2" t="n">
-        <v>0.320530292553533</v>
+        <v>0.1823352153331554</v>
       </c>
       <c r="W2" t="n">
-        <v>0.3199669158655067</v>
+        <v>0.1734019688038801</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3203158121208128</v>
+        <v>0.165828715167902</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.3214269649958986</v>
+        <v>0.1594067313040482</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.3231757237150411</v>
+        <v>0.1539579462597709</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.32545836179212</v>
+        <v>0.1493310622269264</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3281883812540772</v>
+        <v>0.1453979326043286</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.331293462463892</v>
+        <v>0.1420502774850747</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.334712960834285</v>
+        <v>0.1391967650332342</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3383958597362176</v>
+        <v>0.1367604558853912</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.34229909981248</v>
+        <v>0.1346765898477135</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3463862164637289</v>
+        <v>0.13289068497826</v>
       </c>
       <c r="AH2" t="n">
         <v>16</v>
@@ -737,100 +737,100 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.314234768480752</v>
+        <v>1.553981208626474</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5447688988255798</v>
+        <v>0.5284407764425033</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5104801694030021</v>
+        <v>0.4985126471107749</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4868769784224525</v>
+        <v>0.4794106093097229</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4606390846607189</v>
+        <v>0.4557323259324483</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4325025021917865</v>
+        <v>0.4278843581251832</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4044292895265057</v>
+        <v>0.3982981400543461</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3778700168240783</v>
+        <v>0.3690311547844578</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3536344623910783</v>
+        <v>0.3414104922372546</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3320602781645163</v>
+        <v>0.316153817586576</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3131864546311495</v>
+        <v>0.2935553972364824</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2968812299929728</v>
+        <v>0.2736414258069748</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2829267185998864</v>
+        <v>0.2562815512842687</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2710714695974329</v>
+        <v>0.24126349880302</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2610612766057014</v>
+        <v>0.2283406344135969</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2526559488141787</v>
+        <v>0.2172608891083086</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2456373643286251</v>
+        <v>0.2077833244487171</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2398123211584324</v>
+        <v>0.1996867501074319</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2350124370291578</v>
+        <v>0.1927733848390138</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2310924999516313</v>
+        <v>0.1868695412402799</v>
       </c>
       <c r="V3" t="n">
-        <v>0.227928116809983</v>
+        <v>0.1818246180577616</v>
       </c>
       <c r="W3" t="n">
-        <v>0.225413153151369</v>
+        <v>0.1775092143815145</v>
       </c>
       <c r="X3" t="n">
-        <v>0.2234572361893892</v>
+        <v>0.1738128690619672</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.2219834581205256</v>
+        <v>0.1706417257715429</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.220926336925498</v>
+        <v>0.1679162938382262</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.2202300463385789</v>
+        <v>0.1655693928683696</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2198469023359956</v>
+        <v>0.1635443186685883</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.2197360818587527</v>
+        <v>0.1617932379458031</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.2198625452338483</v>
+        <v>0.1602758023164883</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.2201961336093174</v>
+        <v>0.1589579634212626</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.2207108146841559</v>
+        <v>0.1578109672419652</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.221384052918648</v>
+        <v>0.1568105050046121</v>
       </c>
       <c r="AH3" t="n">
         <v>16</v>
@@ -852,100 +852,100 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.934772934575689</v>
+        <v>6.489156517089423</v>
       </c>
       <c r="C4" t="n">
-        <v>1.007719505038147</v>
+        <v>1.267283374045878</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9759781040401271</v>
+        <v>1.110130545568488</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9399670557921647</v>
+        <v>1.061878169080019</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8838717848881338</v>
+        <v>1.016057677966901</v>
       </c>
       <c r="G4" t="n">
-        <v>0.815279723963418</v>
+        <v>0.9557262609785748</v>
       </c>
       <c r="H4" t="n">
-        <v>0.742577756999522</v>
+        <v>0.8842073840524134</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6715505071137688</v>
+        <v>0.8076780827984456</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6055470103179397</v>
+        <v>0.731132769890233</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5462023803317162</v>
+        <v>0.6578891704693316</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4940593250433994</v>
+        <v>0.5898904940820601</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4490084204356355</v>
+        <v>0.5280989575080288</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4105796898479269</v>
+        <v>0.4728216065536806</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3781285707972386</v>
+        <v>0.4239501236860387</v>
       </c>
       <c r="P4" t="n">
-        <v>0.350950531259685</v>
+        <v>0.3811286867760342</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3283486973068694</v>
+        <v>0.3438679041907288</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3096711473527168</v>
+        <v>0.3116200871821966</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2943290461092725</v>
+        <v>0.2838274488704053</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2818030143060059</v>
+        <v>0.2599516635253148</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2716425662850628</v>
+        <v>0.2394907962037542</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2634617239481688</v>
+        <v>0.2219878303271557</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2569327669681482</v>
+        <v>0.2070337362669665</v>
       </c>
       <c r="X4" t="n">
-        <v>0.251779321234631</v>
+        <v>0.1942671088446775</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.2477694931951208</v>
+        <v>0.1833717547841994</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.244709440186389</v>
+        <v>0.1740731570221095</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.2424375668607297</v>
+        <v>0.1661344261653221</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.2408194153087985</v>
+        <v>0.1593521303845705</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.2397432444527349</v>
+        <v>0.153552245001374</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.2391162546436677</v>
+        <v>0.1485863614917082</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.2388613941289036</v>
+        <v>0.1443282280072629</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.2389146772450858</v>
+        <v>0.1406706494498146</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.2392229446972982</v>
+        <v>0.1375227472986001</v>
       </c>
       <c r="AH4" t="n">
         <v>16</v>
@@ -967,100 +967,100 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.58409859514162</v>
+        <v>4.718271242952172</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9531116298277844</v>
+        <v>0.9219841393312097</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9698567637111328</v>
+        <v>0.9341672465288628</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9251346772339423</v>
+        <v>0.9204183828997665</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8504807086658286</v>
+        <v>0.8804759656657428</v>
       </c>
       <c r="G5" t="n">
-        <v>0.765303516401901</v>
+        <v>0.8228800910848627</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6803590432570727</v>
+        <v>0.7558874731976124</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6011735926477743</v>
+        <v>0.6857356267629769</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5302231746818828</v>
+        <v>0.6166300889615917</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4682503764276918</v>
+        <v>0.5511693154293417</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4150489352351606</v>
+        <v>0.4907943601714395</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3699295203163969</v>
+        <v>0.4361568226250885</v>
       </c>
       <c r="N5" t="n">
-        <v>0.331993890963553</v>
+        <v>0.3873933235490351</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3002927524382322</v>
+        <v>0.3443208208098613</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2739126850701301</v>
+        <v>0.3065713081025584</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2520199993043686</v>
+        <v>0.2736822586322873</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2338788348973731</v>
+        <v>0.2451556534973472</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2188543242313999</v>
+        <v>0.2204951543254048</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2064075555709097</v>
+        <v>0.1992283359191641</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1960864780004438</v>
+        <v>0.1809188905501634</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1875152373164457</v>
+        <v>0.1651722439605272</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1803833836336459</v>
+        <v>0.1516369629739101</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1744357331526714</v>
+        <v>0.1400035807003764</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1694632605568035</v>
+        <v>0.1300019345739942</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.1652951549971586</v>
+        <v>0.1213977421703371</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1617920327556787</v>
+        <v>0.1139888837245386</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1588402249535539</v>
+        <v>0.1076016849998842</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.1563470240339072</v>
+        <v>0.1020873755742982</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.1542367620055518</v>
+        <v>0.09731881855647442</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.1524475962649642</v>
+        <v>0.09318755605012564</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.1509288887430664</v>
+        <v>0.08960118177584064</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.1496390771898086</v>
+        <v>0.08648103211725046</v>
       </c>
       <c r="AH5" t="n">
         <v>14</v>
@@ -1082,100 +1082,100 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.105199178108309</v>
+        <v>1.22030857473129</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4605475534941417</v>
+        <v>0.4281400370076412</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4281766757085085</v>
+        <v>0.4161238450029135</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4067914020058724</v>
+        <v>0.4009349037754339</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3836202248566478</v>
+        <v>0.3802049928604711</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3595483371065194</v>
+        <v>0.3565480939317985</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3363169755019801</v>
+        <v>0.332437777606829</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3150561064581976</v>
+        <v>0.3095114783411987</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2962789774798656</v>
+        <v>0.2886577410719023</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2800935382810505</v>
+        <v>0.270244265711264</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2663809048498861</v>
+        <v>0.2543166151482426</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2549130959622938</v>
+        <v>0.2407395741254869</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2454232948773588</v>
+        <v>0.2292890501666112</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2376446961777461</v>
+        <v>0.2197082760059964</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2313300171533023</v>
+        <v>0.2117401818010023</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2262596911117887</v>
+        <v>0.2051446031756984</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2222437679978893</v>
+        <v>0.1997062084415189</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2191205556038367</v>
+        <v>0.1952369747564933</v>
       </c>
       <c r="T6" t="n">
-        <v>0.216753770672107</v>
+        <v>0.1915756315069941</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2150291915844145</v>
+        <v>0.1885855566863644</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2138513380949708</v>
+        <v>0.1861520120832403</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2131404313888102</v>
+        <v>0.1841792251992365</v>
       </c>
       <c r="X6" t="n">
-        <v>0.212829733998767</v>
+        <v>0.1825875925856546</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.2128632862131625</v>
+        <v>0.1813111385923959</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.2131940141529282</v>
+        <v>0.1802952810945418</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.213782166821149</v>
+        <v>0.179494909457505</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.2145940344447236</v>
+        <v>0.1788727556960713</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.2156009020693608</v>
+        <v>0.1783980285749321</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.2167781970478525</v>
+        <v>0.1780452767473918</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.2181047947929174</v>
+        <v>0.1777934475338861</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.2195624529081835</v>
+        <v>0.1776251105523066</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.2211353490650831</v>
+        <v>0.1775258189212396</v>
       </c>
       <c r="AH6" t="n">
         <v>17</v>
@@ -1197,100 +1197,100 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.494694325071687</v>
+        <v>3.784380218124784</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8103054442312978</v>
+        <v>0.8227248456181198</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8026083785712205</v>
+        <v>0.7935869419606703</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7569213781460278</v>
+        <v>0.7548464384254783</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6940165690701836</v>
+        <v>0.7013997712791005</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6257198151214349</v>
+        <v>0.6397539513879894</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5588519518150488</v>
+        <v>0.576185491814207</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4970609247775398</v>
+        <v>0.5150004623931794</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4419966582897891</v>
+        <v>0.4586794117712816</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3941067974959526</v>
+        <v>0.4083845564551956</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3531596317696147</v>
+        <v>0.3644231104160922</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3185754692100524</v>
+        <v>0.3265910152855845</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2896288417609429</v>
+        <v>0.2944070162365739</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2655664044083867</v>
+        <v>0.2672637397159022</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2456713389881339</v>
+        <v>0.2445206281736662</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2292947718055707</v>
+        <v>0.225557894683127</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2158675359016666</v>
+        <v>0.2098051954830273</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2049007594986396</v>
+        <v>0.1967544233327348</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1959805568571132</v>
+        <v>0.1859629022349021</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1887600166323481</v>
+        <v>0.1770510838026508</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1829503543368977</v>
+        <v>0.169697361019414</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1783122629047983</v>
+        <v>0.1636316233006615</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1746479848260143</v>
+        <v>0.1586285251800596</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.1717943250797488</v>
+        <v>0.1545010202739229</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.1696166499569831</v>
+        <v>0.1510944460410861</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.1680038232916343</v>
+        <v>0.1482812807976503</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.1668639867924875</v>
+        <v>0.1459565969099991</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.1661210749073684</v>
+        <v>0.1440341792314842</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.165711954361175</v>
+        <v>0.1424432498437008</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.1655840864788848</v>
+        <v>0.1411257286228481</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.1656936220327402</v>
+        <v>0.1400339573379205</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.1660038509935035</v>
+        <v>0.1391288185964692</v>
       </c>
       <c r="AH7" t="n">
         <v>2</v>
@@ -1312,100 +1312,100 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.241343344019356</v>
+        <v>1.525721399349406</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6245005535737032</v>
+        <v>0.6816016896648982</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5673284358136258</v>
+        <v>0.5569733143793345</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5501208561291734</v>
+        <v>0.5293382766113583</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5327771015588795</v>
+        <v>0.5142387862636816</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5119090619871813</v>
+        <v>0.4970596541858389</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4887033506646332</v>
+        <v>0.4761529222323287</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4646406639966931</v>
+        <v>0.4525996290794832</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4408130482115212</v>
+        <v>0.4277554500156528</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4179258294939565</v>
+        <v>0.4027161392575212</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3963955227950076</v>
+        <v>0.3782570031643199</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3764381772899347</v>
+        <v>0.3548830793533438</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3581354053560593</v>
+        <v>0.332895030870906</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3414814080499118</v>
+        <v>0.3124467647750749</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3264158275394822</v>
+        <v>0.2935905005052419</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3128463736594413</v>
+        <v>0.2763103797557256</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3006641598931506</v>
+        <v>0.2605468659145201</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2897538849704167</v>
+        <v>0.2462141120393969</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2800004038493556</v>
+        <v>0.2332121005399166</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2712927974746935</v>
+        <v>0.2214349587631895</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2635267331190126</v>
+        <v>0.210776512259541</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2566056758524737</v>
+        <v>0.2011338651808176</v>
       </c>
       <c r="X8" t="n">
-        <v>0.2504413443163409</v>
+        <v>0.1924095882267772</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.2449536837474505</v>
+        <v>0.1845129371569336</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.2400705435343155</v>
+        <v>0.1773604077733529</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.2357271860557996</v>
+        <v>0.1708758468664019</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.2318657111520454</v>
+        <v>0.1649902752713078</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.2284344511427129</v>
+        <v>0.1596415330180524</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.2253873710743921</v>
+        <v>0.1547738230999262</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.2226834951259183</v>
+        <v>0.150337206280586</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.2202863708767313</v>
+        <v>0.1462870821044654</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.2181635770618685</v>
+        <v>0.142583679017202</v>
       </c>
       <c r="AH8" t="n">
         <v>18</v>
@@ -1427,100 +1427,100 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.528336312020059</v>
+        <v>1.912292588005119</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6431251779754508</v>
+        <v>0.6005383923147036</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6250459339546692</v>
+        <v>0.5855610809798648</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5893362236314295</v>
+        <v>0.5654174474297222</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5475427247402423</v>
+        <v>0.538408772019348</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5065481117604358</v>
+        <v>0.5083518936325411</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4695602826782315</v>
+        <v>0.4784818731819515</v>
       </c>
       <c r="I9" t="n">
-        <v>0.437708298823579</v>
+        <v>0.4507753366188215</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4110276313683707</v>
+        <v>0.4261823490622684</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3890400227738748</v>
+        <v>0.4049817426463208</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3710768784979259</v>
+        <v>0.3870648059745154</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3564486797992683</v>
+        <v>0.3721265043632114</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3445253788917951</v>
+        <v>0.3597835493585378</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3347673593239966</v>
+        <v>0.3496422502304954</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3267304228904783</v>
+        <v>0.341334255451138</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3200583176475476</v>
+        <v>0.3345327797536579</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3144703157954611</v>
+        <v>0.3289575473100376</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3097478023992256</v>
+        <v>0.3243736126516501</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3057217938665148</v>
+        <v>0.3205871849167157</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3022621690985832</v>
+        <v>0.3174402781457119</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2992687945894839</v>
+        <v>0.3148051995996849</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2966644306139236</v>
+        <v>0.3125793967372429</v>
       </c>
       <c r="X9" t="n">
-        <v>0.294389182815693</v>
+        <v>0.3106808945034177</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.2923962317531344</v>
+        <v>0.3090443911639527</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.2906485861042757</v>
+        <v>0.3076179937868986</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.2891166375234722</v>
+        <v>0.3063605325669407</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.2877763328290737</v>
+        <v>0.3052393772428014</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.2866078154577642</v>
+        <v>0.3042286771331793</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.2855944199791396</v>
+        <v>0.3033079518016222</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.2847219300258608</v>
+        <v>0.3024609679807029</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.2839780313980522</v>
+        <v>0.3016748478613236</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.2833519089407075</v>
+        <v>0.3009393629831197</v>
       </c>
       <c r="AH9" t="n">
         <v>16</v>
@@ -1542,100 +1542,100 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.92494768016994</v>
+        <v>1.525059727217569</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5906960544548164</v>
+        <v>0.5081818206168259</v>
       </c>
       <c r="D10" t="n">
-        <v>0.490000396921125</v>
+        <v>0.4445659632877415</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4275433982928046</v>
+        <v>0.3918183721802213</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3767338931784039</v>
+        <v>0.3465359674914876</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3360199467461207</v>
+        <v>0.3088632383490508</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3045671228704072</v>
+        <v>0.2786070898546275</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2810541130161537</v>
+        <v>0.2549935814041263</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2639391766160543</v>
+        <v>0.2369454190512369</v>
       </c>
       <c r="K10" t="n">
-        <v>0.251756702576424</v>
+        <v>0.2233438333696631</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2432611501104276</v>
+        <v>0.213176684120845</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2374623114578489</v>
+        <v>0.20559706482935</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2336060927428337</v>
+        <v>0.1999301939545836</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2311348803927373</v>
+        <v>0.1956558680889734</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2296449772378791</v>
+        <v>0.1923823742045536</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2288486808212735</v>
+        <v>0.1898199418271707</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2285433976126108</v>
+        <v>0.1877572435739615</v>
       </c>
       <c r="S10" t="n">
-        <v>0.228587770296256</v>
+        <v>0.1860420369818487</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2288838422795692</v>
+        <v>0.1845658884065858</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2293640452145784</v>
+        <v>0.1832524504854938</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2299818705579373</v>
+        <v>0.18204863828213</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2307052730787677</v>
+        <v>0.1809180793245331</v>
       </c>
       <c r="X10" t="n">
-        <v>0.2315120584254182</v>
+        <v>0.1798363026726106</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.2323866894070534</v>
+        <v>0.1787872349961254</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.2333180945062896</v>
+        <v>0.1777606668237796</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.2342981773718636</v>
+        <v>0.1767504323199764</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.2353208123449198</v>
+        <v>0.175753110110126</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.236381174274962</v>
+        <v>0.1747671024028055</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.2374752964275003</v>
+        <v>0.1737919873975749</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.2385997827162056</v>
+        <v>0.1728280682024382</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.2397516233707605</v>
+        <v>0.171876062396321</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.2409280791702261</v>
+        <v>0.1709368917466707</v>
       </c>
       <c r="AH10" t="n">
         <v>12</v>
@@ -1657,100 +1657,100 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9.951688587009437</v>
+        <v>10.48030634877312</v>
       </c>
       <c r="C11" t="n">
-        <v>1.355481034165546</v>
+        <v>1.423869586093617</v>
       </c>
       <c r="D11" t="n">
-        <v>1.403066999067167</v>
+        <v>1.478634511325085</v>
       </c>
       <c r="E11" t="n">
-        <v>1.348756104107439</v>
+        <v>1.459721617533117</v>
       </c>
       <c r="F11" t="n">
-        <v>1.243329176593027</v>
+        <v>1.385903925623568</v>
       </c>
       <c r="G11" t="n">
-        <v>1.117936677705032</v>
+        <v>1.28030022902891</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9902996159354657</v>
+        <v>1.16038083488853</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8699176897215578</v>
+        <v>1.037828689870015</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7613506327912339</v>
+        <v>0.9198499082564976</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6662504946592041</v>
+        <v>0.8105063573742134</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5846155437876791</v>
+        <v>0.7117598903073025</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5155609436926459</v>
+        <v>0.6242247410625589</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4577869906873881</v>
+        <v>0.5476886118054548</v>
       </c>
       <c r="O11" t="n">
-        <v>0.409857004483509</v>
+        <v>0.4814642846594301</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3703555645866636</v>
+        <v>0.4246213687523898</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3379722096590568</v>
+        <v>0.3761350019232514</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3115395323656954</v>
+        <v>0.3349779178708681</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2900441876833965</v>
+        <v>0.3001744774005611</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2726225706994947</v>
+        <v>0.2708295989780058</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2585485188623475</v>
+        <v>0.2461414906148257</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2472175375025532</v>
+        <v>0.2254042442757072</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2381302078903706</v>
+        <v>0.2080043694733551</v>
       </c>
       <c r="X11" t="n">
-        <v>0.2308762667496131</v>
+        <v>0.1934139667435311</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.225120114749636</v>
+        <v>0.1811822951043679</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.2205880659861476</v>
+        <v>0.1709268422191169</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.2170573892021167</v>
+        <v>0.1623245707065016</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.214347047270883</v>
+        <v>0.1551037244654444</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.212309970096116</v>
+        <v>0.1490363896520753</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.2108266688198926</v>
+        <v>0.1439318842757986</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.2097999975731987</v>
+        <v>0.1396309760846842</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.209150881244016</v>
+        <v>0.1360008850909029</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.2088148466249111</v>
+        <v>0.1329310041227862</v>
       </c>
       <c r="AH11" t="n">
         <v>12</v>
@@ -1772,100 +1772,100 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.755241458893001</v>
+        <v>2.173186235785926</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5966140797306234</v>
+        <v>0.6667607641136131</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5897007395699101</v>
+        <v>0.5893247666044834</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5728128764019731</v>
+        <v>0.5690852809319142</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5451014478695334</v>
+        <v>0.551067091738432</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5113437048189426</v>
+        <v>0.5263772430328965</v>
       </c>
       <c r="H12" t="n">
-        <v>0.475546156871341</v>
+        <v>0.495682102453557</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4402769143587072</v>
+        <v>0.4613903475721912</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4069943973438974</v>
+        <v>0.4257072410962804</v>
       </c>
       <c r="K12" t="n">
-        <v>0.376430358406612</v>
+        <v>0.3902637979291303</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3488674180008445</v>
+        <v>0.3561502486641436</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3243209509791192</v>
+        <v>0.3240343122422679</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3026548700513342</v>
+        <v>0.2942774161041222</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2836543265729972</v>
+        <v>0.2670285948284147</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2670706491489304</v>
+        <v>0.2422950145452188</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.2526484238488708</v>
+        <v>0.219993020367867</v>
       </c>
       <c r="R12" t="n">
-        <v>0.24014112807622</v>
+        <v>0.1999842082415212</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2293194946953328</v>
+        <v>0.1821004075294242</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2199753347533535</v>
+        <v>0.166160624903247</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2119225973531205</v>
+        <v>0.151982244637909</v>
       </c>
       <c r="V12" t="n">
-        <v>0.204996817795093</v>
+        <v>0.1393881740908755</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1990536897959186</v>
+        <v>0.1282111605753862</v>
       </c>
       <c r="X12" t="n">
-        <v>0.1939672234151564</v>
+        <v>0.118296161787658</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.1896277704986533</v>
+        <v>0.1095013996505672</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.185940082707069</v>
+        <v>0.101698544028629</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.1828214924888186</v>
+        <v>0.09477234024538961</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.1802002604769895</v>
+        <v>0.08861989904224586</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.1780141041750176</v>
+        <v>0.08314979940931071</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.1762089060306712</v>
+        <v>0.07828110613402102</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.1747375898049194</v>
+        <v>0.07394236950242987</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.1735591496919285</v>
+        <v>0.07007065038658271</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.1726378150848897</v>
+        <v>0.06661059708148542</v>
       </c>
       <c r="AH12" t="n">
         <v>14</v>
@@ -1887,100 +1887,100 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.443035458073032</v>
+        <v>4.440111300188888</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8897395470202497</v>
+        <v>0.937982506382653</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9209320023039542</v>
+        <v>0.9489127313609217</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9083173058568835</v>
+        <v>0.951859915844962</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8690996787660207</v>
+        <v>0.9329050500133049</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8158666864175544</v>
+        <v>0.8954350849033549</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7565965320227649</v>
+        <v>0.8456672487482905</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6962694966556963</v>
+        <v>0.7891759865298795</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6378923855515403</v>
+        <v>0.7301672421594126</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5831694791006954</v>
+        <v>0.6715614291620222</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5329531201374844</v>
+        <v>0.6152596581863085</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4875495716908959</v>
+        <v>0.5624091748103403</v>
       </c>
       <c r="N13" t="n">
-        <v>0.4469262906069773</v>
+        <v>0.513621698984104</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4108510969469529</v>
+        <v>0.4691404713950584</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3789842461134751</v>
+        <v>0.4289634704287601</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.3509381007842152</v>
+        <v>0.3929322017913837</v>
       </c>
       <c r="R13" t="n">
-        <v>0.3263147051933609</v>
+        <v>0.3607944871859897</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3047284583905291</v>
+        <v>0.3322480475866434</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2858188834320641</v>
+        <v>0.3069701133157232</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2692569359719589</v>
+        <v>0.2846369923684779</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2547472038257603</v>
+        <v>0.2649365073563112</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2420275860664124</v>
+        <v>0.2475754329177895</v>
       </c>
       <c r="X13" t="n">
-        <v>0.2308675105256177</v>
+        <v>0.2322834816523753</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.2210653836058476</v>
+        <v>0.218814953532818</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.2124457169900277</v>
+        <v>0.2069488449561804</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.2048562072427469</v>
+        <v>0.1964879804482521</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.1981649316912989</v>
+        <v>0.1872575605491141</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.1922577499252891</v>
+        <v>0.1791033969463676</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.1870359525415765</v>
+        <v>0.1718900180259392</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.1824141688707573</v>
+        <v>0.1654987654031704</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.1783185274521955</v>
+        <v>0.1598259578090026</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.1746850529164094</v>
+        <v>0.1547811678694236</v>
       </c>
       <c r="AH13" t="n">
         <v>15</v>
@@ -2002,100 +2002,100 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.411310976196819</v>
+        <v>0.8954318155397425</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4712376503217907</v>
+        <v>0.4312444650952366</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4509049245938175</v>
+        <v>0.4068109252573663</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4571093193338244</v>
+        <v>0.4115805270170788</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4641574469563947</v>
+        <v>0.4180056587354191</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4676006929599859</v>
+        <v>0.4201795078848069</v>
       </c>
       <c r="H14" t="n">
-        <v>0.467390590553473</v>
+        <v>0.4177414677197103</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4643061949183494</v>
+        <v>0.4116643787366497</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4591147970685507</v>
+        <v>0.4030324691714344</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4524265183669715</v>
+        <v>0.3927413759345209</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4447053410087308</v>
+        <v>0.3814653308325204</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4363041587319833</v>
+        <v>0.3696921706625113</v>
       </c>
       <c r="N14" t="n">
-        <v>0.4274947356724081</v>
+        <v>0.3577673052150467</v>
       </c>
       <c r="O14" t="n">
-        <v>0.418488971001757</v>
+        <v>0.3459312289122224</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4094533040344762</v>
+        <v>0.3343482585421659</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.4005185365425861</v>
+        <v>0.3231276976452023</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3917867711257292</v>
+        <v>0.312339207249475</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3833365616473479</v>
+        <v>0.3020239359266171</v>
       </c>
       <c r="T14" t="n">
-        <v>0.375226936287901</v>
+        <v>0.2922025938603935</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3675006763899125</v>
+        <v>0.2828813310022861</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3601870691626423</v>
+        <v>0.2740560325355034</v>
       </c>
       <c r="W14" t="n">
-        <v>0.3533042586960692</v>
+        <v>0.2657154671901761</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3468612688722049</v>
+        <v>0.2578435987114441</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.3408597452666137</v>
+        <v>0.2504212829737554</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.335295449881407</v>
+        <v>0.2434275115179741</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.3301595361040463</v>
+        <v>0.2368403186285234</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.3254396280738656</v>
+        <v>0.230637437923781</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.3211207267799603</v>
+        <v>0.2247967720158764</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.3171859637887983</v>
+        <v>0.2192967225156416</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.3136172221083957</v>
+        <v>0.2141164157342607</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.3103956422073735</v>
+        <v>0.2092358506313406</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.3075020296172405</v>
+        <v>0.2046359890165171</v>
       </c>
       <c r="AH14" t="n">
         <v>15</v>
@@ -2117,100 +2117,100 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9544485585802924</v>
+        <v>1.191251305869328</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4173967248009387</v>
+        <v>0.4022776201334004</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4199645711828774</v>
+        <v>0.422375774035851</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4257435136908002</v>
+        <v>0.4305608742038471</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4242020003713242</v>
+        <v>0.4268422828773142</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4165722341634971</v>
+        <v>0.4150244237389881</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4051290788946195</v>
+        <v>0.3985056571532045</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3916875358620174</v>
+        <v>0.3797558690202597</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3774835321990711</v>
+        <v>0.3604173813561657</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3633064041253822</v>
+        <v>0.3415156516903389</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3496374344862533</v>
+        <v>0.3236473515107933</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3367540081269401</v>
+        <v>0.3071227957312232</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3248013944813987</v>
+        <v>0.2920671946702906</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3138406306197032</v>
+        <v>0.2784902977957925</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3038799919316839</v>
+        <v>0.2663332357963353</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.2948955101062661</v>
+        <v>0.25549941569694</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2868442761072607</v>
+        <v>0.2458744718121313</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2796730198125392</v>
+        <v>0.2373388109267843</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2733236063666535</v>
+        <v>0.2297752096983511</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2677365219607823</v>
+        <v>0.2230731513197201</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2628530486961071</v>
+        <v>0.2171310484110461</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2586165845926129</v>
+        <v>0.2118571251211205</v>
       </c>
       <c r="X15" t="n">
-        <v>0.2549734063177546</v>
+        <v>0.2071694745507885</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.2518730692303883</v>
+        <v>0.2029956323544304</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.2492685723956184</v>
+        <v>0.1992718885414038</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.2471163726306263</v>
+        <v>0.1959424794481308</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.2453763031574548</v>
+        <v>0.1929587483313364</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.2440114337450192</v>
+        <v>0.1902783275814746</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.2429878968858446</v>
+        <v>0.1878643723519844</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.2422746963584303</v>
+        <v>0.1856848604550767</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.2418435090437275</v>
+        <v>0.1837119639623796</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.2416684871686687</v>
+        <v>0.1819214922128729</v>
       </c>
       <c r="AH15" t="n">
         <v>11</v>
@@ -2232,100 +2232,100 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9.49032692480051</v>
+        <v>13.36261544414117</v>
       </c>
       <c r="C16" t="n">
-        <v>1.158081950839932</v>
+        <v>1.460470179064191</v>
       </c>
       <c r="D16" t="n">
-        <v>1.203343846392542</v>
+        <v>1.455137878349631</v>
       </c>
       <c r="E16" t="n">
-        <v>1.155174068711695</v>
+        <v>1.422657760649867</v>
       </c>
       <c r="F16" t="n">
-        <v>1.061104883584046</v>
+        <v>1.34356921131604</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9487164841560736</v>
+        <v>1.233163919868276</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8338994625228207</v>
+        <v>1.107819301077581</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7253863781953054</v>
+        <v>0.9795567996328746</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6275007988702328</v>
+        <v>0.8560566461934387</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5419016042023046</v>
+        <v>0.7417205856910354</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4686949932770385</v>
+        <v>0.6386982181188726</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4071371829539057</v>
+        <v>0.5476749650470706</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3560708444376222</v>
+        <v>0.4684318939638169</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3141890072805539</v>
+        <v>0.4002280904947688</v>
       </c>
       <c r="P16" t="n">
-        <v>0.28018817911093</v>
+        <v>0.3420543717418625</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.2528513195756636</v>
+        <v>0.292796766239683</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2310872872003625</v>
+        <v>0.2513380277172027</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2139440572680695</v>
+        <v>0.2166173438167082</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2006068248271185</v>
+        <v>0.1876623665094599</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1903880221968228</v>
+        <v>0.1636033346674398</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1827136004850363</v>
+        <v>0.1436759659302151</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1771081829288376</v>
+        <v>0.1272176222508999</v>
       </c>
       <c r="X16" t="n">
-        <v>0.1731805801108355</v>
+        <v>0.1136597407849669</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.1706104518731232</v>
+        <v>0.1025184775895536</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.1691364661115238</v>
+        <v>0.09338479756345743</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.1685460456473535</v>
+        <v>0.08591476119660102</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.1686666478723631</v>
+        <v>0.07982043667084622</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.1693584460977143</v>
+        <v>0.07486165493465753</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.1705082491600176</v>
+        <v>0.07083869057681599</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.1720244891275216</v>
+        <v>0.06758586815638777</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.1738331145925064</v>
+        <v>0.06496604505386859</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.1758742419438062</v>
+        <v>0.06286589609302151</v>
       </c>
       <c r="AH16" t="n">
         <v>16</v>
@@ -2347,100 +2347,100 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4.144298716520192</v>
+        <v>2.657126460129096</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8448508799131975</v>
+        <v>0.8936995656726607</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8152388784218623</v>
+        <v>0.7435884692784388</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7753237628953994</v>
+        <v>0.7013737439057115</v>
       </c>
       <c r="F17" t="n">
-        <v>0.72231290434147</v>
+        <v>0.6728579589069937</v>
       </c>
       <c r="G17" t="n">
-        <v>0.663823554916093</v>
+        <v>0.6405758440007245</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6058299168438067</v>
+        <v>0.6035358122939819</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5517387908301944</v>
+        <v>0.5638915545571344</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5031198199046646</v>
+        <v>0.5238023484589844</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4604340758851759</v>
+        <v>0.4848413298596</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4235272076617808</v>
+        <v>0.4480089154410293</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3919326296805979</v>
+        <v>0.4138648864539845</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3650509452484591</v>
+        <v>0.3826586564496647</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3422528572512945</v>
+        <v>0.3544324328526528</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3229354575817446</v>
+        <v>0.3290968265188728</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.3065503537724269</v>
+        <v>0.3064841175852708</v>
       </c>
       <c r="R17" t="n">
-        <v>0.292615039100968</v>
+        <v>0.2863847534760447</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2807145805340149</v>
+        <v>0.2685717155490137</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2704980067421543</v>
+        <v>0.2528162990025237</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2616720851481149</v>
+        <v>0.2388979149656031</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2539941046676094</v>
+        <v>0.2266097954408515</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2472646017412335</v>
+        <v>0.2157619383890353</v>
       </c>
       <c r="X17" t="n">
-        <v>0.2413205403690504</v>
+        <v>0.20618223363013</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.2360291926293935</v>
+        <v>0.1977164245523702</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.2312828067953337</v>
+        <v>0.1902273567283256</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.2269940579616677</v>
+        <v>0.1835938201014475</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.2230922263815759</v>
+        <v>0.17770918980322</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.2195200253481345</v>
+        <v>0.1724799997128914</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.2162309929540465</v>
+        <v>0.1678245337462463</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.2131873636789878</v>
+        <v>0.1636714861920568</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.2103583422183414</v>
+        <v>0.1599587196399341</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.2077187106370699</v>
+        <v>0.1566321339004426</v>
       </c>
       <c r="AH17" t="n">
         <v>17</v>
@@ -2462,100 +2462,100 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18.02302992750311</v>
+        <v>21.39703485798301</v>
       </c>
       <c r="C18" t="n">
-        <v>1.478139961878701</v>
+        <v>1.717790416190809</v>
       </c>
       <c r="D18" t="n">
-        <v>1.595450746412772</v>
+        <v>1.82284508907203</v>
       </c>
       <c r="E18" t="n">
-        <v>1.573589477716824</v>
+        <v>1.827434287832653</v>
       </c>
       <c r="F18" t="n">
-        <v>1.475098993967174</v>
+        <v>1.750553330090187</v>
       </c>
       <c r="G18" t="n">
-        <v>1.339406422333548</v>
+        <v>1.62341135084641</v>
       </c>
       <c r="H18" t="n">
-        <v>1.190770386349297</v>
+        <v>1.470868797807916</v>
       </c>
       <c r="I18" t="n">
-        <v>1.043613226080954</v>
+        <v>1.310122059848433</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9059998448311953</v>
+        <v>1.152189957594121</v>
       </c>
       <c r="K18" t="n">
-        <v>0.781940606387815</v>
+        <v>1.003636420712104</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6729180368100574</v>
+        <v>0.8679693549751446</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5788946065496821</v>
+        <v>0.7466723701605127</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4989715393802474</v>
+        <v>0.6399358697771311</v>
       </c>
       <c r="O18" t="n">
-        <v>0.431812739331751</v>
+        <v>0.5471630474394532</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3759111760365764</v>
+        <v>0.4673133032046946</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.3297503895228597</v>
+        <v>0.3991304335209532</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2918969828052003</v>
+        <v>0.3412902387586535</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2610484591547353</v>
+        <v>0.2924924665808188</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2360528450586553</v>
+        <v>0.2515148262712775</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2159110971633612</v>
+        <v>0.2172415905864381</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1997695593407871</v>
+        <v>0.188675545215222</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1869071894784826</v>
+        <v>0.1649393593634227</v>
       </c>
       <c r="X18" t="n">
-        <v>0.1767205504597275</v>
+        <v>0.1452705405441544</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.1687084023437326</v>
+        <v>0.1290127861854731</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.1624569659817203</v>
+        <v>0.1156055964849206</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.157626428825972</v>
+        <v>0.1045733526055669</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.1539389456862574</v>
+        <v>0.09551460903455018</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.1511681911868874</v>
+        <v>0.08809203900245854</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.1491304056631057</v>
+        <v>0.08202326434856613</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.1476768141000671</v>
+        <v>0.07707266533239253</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.1466872693500329</v>
+        <v>0.07304417965719379</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.1460649633966867</v>
+        <v>0.0697750477629875</v>
       </c>
       <c r="AH18" t="n">
         <v>17</v>
@@ -2577,100 +2577,100 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.403314176985833</v>
+        <v>1.693759103435931</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9133635925954162</v>
+        <v>1.227732930576797</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7254219626329027</v>
+        <v>0.7123092475745376</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6485093679609273</v>
+        <v>0.5846775220450978</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5934985100492826</v>
+        <v>0.5340405454690281</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5437669149053264</v>
+        <v>0.4986158213435204</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4975710981683419</v>
+        <v>0.4655556066898501</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4554897190953231</v>
+        <v>0.4330663179654394</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4179610784483967</v>
+        <v>0.4015922639958365</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3850254094171074</v>
+        <v>0.3717918788836396</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3564438222645407</v>
+        <v>0.3441233369507824</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3318288143692424</v>
+        <v>0.3188158151001619</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3107338259131285</v>
+        <v>0.2959226061047665</v>
       </c>
       <c r="O19" t="n">
-        <v>0.292707243006489</v>
+        <v>0.2753794499344519</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2773223513105274</v>
+        <v>0.2570509399253588</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.264192145873251</v>
+        <v>0.2407636748151316</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2529749488009149</v>
+        <v>0.2263285945176243</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2433746578255444</v>
+        <v>0.2135553345979614</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2351380428510828</v>
+        <v>0.2022609731450672</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2280505955889527</v>
+        <v>0.1922749614184282</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2219318477859541</v>
+        <v>0.1834415270416762</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2166306938982556</v>
+        <v>0.175620451569934</v>
       </c>
       <c r="X19" t="n">
-        <v>0.2120210119922818</v>
+        <v>0.1686868410956404</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.2079977249956872</v>
+        <v>0.1625303069823586</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.2044733520182026</v>
+        <v>0.1570538328374756</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.20137504554979</v>
+        <v>0.1521725065460805</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.1986420810643749</v>
+        <v>0.1478122298434025</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.1962237517008781</v>
+        <v>0.143908473209359</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.1940776161923677</v>
+        <v>0.1404051141810054</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.1921680491258494</v>
+        <v>0.1372533778037596</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.1904650464230274</v>
+        <v>0.134410885594332</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.1889432440691551</v>
+        <v>0.1318408117828235</v>
       </c>
       <c r="AH19" t="n">
         <v>17</v>
@@ -2692,100 +2692,100 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16.24072120988884</v>
+        <v>12.85612337543645</v>
       </c>
       <c r="C20" t="n">
-        <v>1.666947146299011</v>
+        <v>1.57990350577618</v>
       </c>
       <c r="D20" t="n">
-        <v>1.65658235781654</v>
+        <v>1.558948108767136</v>
       </c>
       <c r="E20" t="n">
-        <v>1.538789456733808</v>
+        <v>1.461629653220127</v>
       </c>
       <c r="F20" t="n">
-        <v>1.370631077576201</v>
+        <v>1.319336494884657</v>
       </c>
       <c r="G20" t="n">
-        <v>1.189631352613525</v>
+        <v>1.159546257241563</v>
       </c>
       <c r="H20" t="n">
-        <v>1.016379651717497</v>
+        <v>1.000276560463793</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8607966568999645</v>
+        <v>0.8518659290949123</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7265540585902966</v>
+        <v>0.7193567538489746</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6138615281471551</v>
+        <v>0.6044460563837081</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5211509441529978</v>
+        <v>0.5068646449502164</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4460680026206216</v>
+        <v>0.4252876799325395</v>
       </c>
       <c r="N20" t="n">
-        <v>0.386037757865822</v>
+        <v>0.3579084270680282</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3385708040491045</v>
+        <v>0.3027837491022343</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3014137650161668</v>
+        <v>0.2580304053705378</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.2726084998884037</v>
+        <v>0.2219267151922006</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2504998583088555</v>
+        <v>0.1929560680951954</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2337163484280674</v>
+        <v>0.1698161213721228</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2211383278235874</v>
+        <v>0.1514089345377778</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2118622062359</v>
+        <v>0.1368215665161577</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2051653469393497</v>
+        <v>0.125302909997402</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2004740324562522</v>
+        <v>0.1162401184232892</v>
       </c>
       <c r="X20" t="n">
-        <v>0.1973354799213612</v>
+        <v>0.109136449780309</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.1953941025296837</v>
+        <v>0.1035914041722958</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.1943717908980129</v>
+        <v>0.09928346429447309</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.1940517873962329</v>
+        <v>0.09595542285006931</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.1942656558346307</v>
+        <v>0.09340210841184816</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.1948828508827479</v>
+        <v>0.09146024225831319</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.1958024309440143</v>
+        <v>0.0900001352255001</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.1969465137936543</v>
+        <v>0.08891894138146947</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.1982551339406262</v>
+        <v>0.08813520922849309</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.1996822178044856</v>
+        <v>0.08758450196813472</v>
       </c>
       <c r="AH20" t="n">
         <v>7</v>
@@ -2807,100 +2807,100 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5.278319480373787</v>
+        <v>4.114313901760631</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9218448843066287</v>
+        <v>0.8807458664721913</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9068496903405886</v>
+        <v>0.8595657855823123</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8410221529821716</v>
+        <v>0.8119065896839793</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7567436225141627</v>
+        <v>0.7481543896513124</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6696748835900691</v>
+        <v>0.6772363211366094</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5876040845244203</v>
+        <v>0.6057689037841899</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5140942096003983</v>
+        <v>0.5380079458363446</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4503350641272394</v>
+        <v>0.4762951826214982</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3962135834853445</v>
+        <v>0.42162574942028</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3509545964933207</v>
+        <v>0.3741348775213265</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3135009808414788</v>
+        <v>0.3334564032033107</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2827313899693202</v>
+        <v>0.2989656089436925</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2575772953723006</v>
+        <v>0.2699340114825334</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2370789477846746</v>
+        <v>0.2456224402642448</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.2204055273921912</v>
+        <v>0.2253330508641007</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2068553509265663</v>
+        <v>0.2084351001707341</v>
       </c>
       <c r="S21" t="n">
-        <v>0.195845874840707</v>
+        <v>0.1943746151209496</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1868992937743545</v>
+        <v>0.1826746446442318</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1796270447680419</v>
+        <v>0.1729303867262868</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1737149885426257</v>
+        <v>0.1648018655763508</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1689101120619231</v>
+        <v>0.158005769505369</v>
       </c>
       <c r="X21" t="n">
-        <v>0.1650090574551291</v>
+        <v>0.1523073741322243</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.1618484845350286</v>
+        <v>0.1475130429102391</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.1592971229888319</v>
+        <v>0.143463531018383</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.1572493057114398</v>
+        <v>0.1400281606153458</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.1556197591226743</v>
+        <v>0.1370998461020289</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.1543394366472689</v>
+        <v>0.1345909015718252</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.1533522040983949</v>
+        <v>0.1324295422725775</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.1526122125686528</v>
+        <v>0.1305569868967776</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.1520818212590798</v>
+        <v>0.1289250710573498</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.1517299572913406</v>
+        <v>0.1274942901805362</v>
       </c>
       <c r="AH21" t="n">
         <v>11</v>
@@ -2922,100 +2922,100 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4.589650704735455</v>
+        <v>3.962386120277526</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8511009300726241</v>
+        <v>0.8108069254752412</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8289310954248642</v>
+        <v>0.7938189734909019</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7684860314246281</v>
+        <v>0.7461010878851203</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6903814252067972</v>
+        <v>0.6805572505432089</v>
       </c>
       <c r="G22" t="n">
-        <v>0.609140600178276</v>
+        <v>0.6086073485492837</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5327380399399184</v>
+        <v>0.5378118177074516</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4648689419046632</v>
+        <v>0.4724405203711776</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4067059149770221</v>
+        <v>0.4144616954865768</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3580521017611941</v>
+        <v>0.3644061435465252</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3180435228863356</v>
+        <v>0.3219869665993583</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2855561218248281</v>
+        <v>0.2865041864442681</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2594294583665343</v>
+        <v>0.2570926300331169</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2385803067556811</v>
+        <v>0.232864855410716</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2220522316871018</v>
+        <v>0.212987309036286</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.2090294256473331</v>
+        <v>0.1967157264966952</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1988317983486472</v>
+        <v>0.1834067047279275</v>
       </c>
       <c r="S22" t="n">
-        <v>0.190901271588377</v>
+        <v>0.1725161080745454</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1847849157466072</v>
+        <v>0.1635908296123697</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1801179607754844</v>
+        <v>0.1562577691769047</v>
       </c>
       <c r="V22" t="n">
-        <v>0.1766081778985114</v>
+        <v>0.1502122194204802</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1740222473325903</v>
+        <v>0.1452068255754961</v>
       </c>
       <c r="X22" t="n">
-        <v>0.1721742436009227</v>
+        <v>0.1410416704861349</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.1709161223049893</v>
+        <v>0.1375556807198286</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.1701299812652895</v>
+        <v>0.1346193532302384</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.1697218343258395</v>
+        <v>0.1321287020846754</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.169616641731091</v>
+        <v>0.1300002815653587</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.169754365715866</v>
+        <v>0.1281671309404144</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.1700868518501894</v>
+        <v>0.1265754923988245</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.170575369310141</v>
+        <v>0.1251821681146841</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.1711886734058787</v>
+        <v>0.1239523999722225</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.1719014800493761</v>
+        <v>0.1228581732764039</v>
       </c>
       <c r="AH22" t="n">
         <v>17</v>
@@ -3037,100 +3037,100 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7.281133422132355</v>
+        <v>5.623001079119892</v>
       </c>
       <c r="C23" t="n">
-        <v>1.033895610803379</v>
+        <v>0.9950707168573025</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9987981501341153</v>
+        <v>0.9542554914568638</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9092333322041148</v>
+        <v>0.8851292421518755</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8001571170080803</v>
+        <v>0.7980431857880972</v>
       </c>
       <c r="G23" t="n">
-        <v>0.691457658316962</v>
+        <v>0.7054549751606822</v>
       </c>
       <c r="H23" t="n">
-        <v>0.592702966515427</v>
+        <v>0.6160352069971849</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5076010996492019</v>
+        <v>0.5346548079591906</v>
       </c>
       <c r="J23" t="n">
-        <v>0.436710805674185</v>
+        <v>0.4634320494372818</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3790304949194365</v>
+        <v>0.402762803085237</v>
       </c>
       <c r="L23" t="n">
-        <v>0.332900107105167</v>
+        <v>0.3520780275145596</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2964927131910449</v>
+        <v>0.3103394390689541</v>
       </c>
       <c r="N23" t="n">
-        <v>0.2680654564296032</v>
+        <v>0.2763410025639307</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2460724741664111</v>
+        <v>0.2488802003469401</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2292013610130182</v>
+        <v>0.2268468412189699</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.2163696051650537</v>
+        <v>0.2092619463051477</v>
       </c>
       <c r="R23" t="n">
-        <v>0.206702115604725</v>
+        <v>0.195287807893302</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1995017003756899</v>
+        <v>0.1842224354043818</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1942188342283473</v>
+        <v>0.175486412649916</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1904238250807712</v>
+        <v>0.1686068711688413</v>
       </c>
       <c r="V23" t="n">
-        <v>0.1877826546873881</v>
+        <v>0.1632012104066625</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1860367719149377</v>
+        <v>0.1589619290736344</v>
       </c>
       <c r="X23" t="n">
-        <v>0.1849866129811092</v>
+        <v>0.155643179372231</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.1844784016474598</v>
+        <v>0.1530492244925593</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.1843937168779672</v>
+        <v>0.1510247459251205</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.1846413307622671</v>
+        <v>0.1494468320183537</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.1851508721305747</v>
+        <v>0.1482184334547433</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.1858679370118347</v>
+        <v>0.1472630644213459</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.1867503330871635</v>
+        <v>0.1465205416728888</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.1877652053978753</v>
+        <v>0.1459435764264669</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.1888868423649715</v>
+        <v>0.1454950597688804</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.1900950042677943</v>
+        <v>0.1451459075540926</v>
       </c>
       <c r="AH23" t="n">
         <v>17</v>
@@ -3152,100 +3152,100 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5.005340849180383</v>
+        <v>7.114749051406425</v>
       </c>
       <c r="C24" t="n">
-        <v>1.029895638752001</v>
+        <v>1.148414985258549</v>
       </c>
       <c r="D24" t="n">
-        <v>1.074827421847533</v>
+        <v>1.165198636857612</v>
       </c>
       <c r="E24" t="n">
-        <v>1.051316980783561</v>
+        <v>1.152763766185872</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9921506919746431</v>
+        <v>1.105062464949238</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9170537411372245</v>
+        <v>1.033795094853938</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8373820973526849</v>
+        <v>0.9501843455643755</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7595740213538293</v>
+        <v>0.8624561259903792</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6870922667797411</v>
+        <v>0.7760313682932747</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6215812674501761</v>
+        <v>0.6942113966726862</v>
       </c>
       <c r="L24" t="n">
-        <v>0.563585162817972</v>
+        <v>0.6188125684009387</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5130025087809983</v>
+        <v>0.5506538691565693</v>
       </c>
       <c r="N24" t="n">
-        <v>0.4693751363531459</v>
+        <v>0.4899082412623129</v>
       </c>
       <c r="O24" t="n">
-        <v>0.4320698286456376</v>
+        <v>0.4363479685617125</v>
       </c>
       <c r="P24" t="n">
-        <v>0.4003901266540182</v>
+        <v>0.3895124857507196</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.3736426829254104</v>
+        <v>0.3488208901172752</v>
       </c>
       <c r="R24" t="n">
-        <v>0.351174333092193</v>
+        <v>0.3136456415007446</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3323906113136034</v>
+        <v>0.2833593442033878</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3167627935527058</v>
+        <v>0.2573630805559662</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3038281062443394</v>
+        <v>0.2351022767485819</v>
       </c>
       <c r="V24" t="n">
-        <v>0.2931860972062402</v>
+        <v>0.2160742936512806</v>
       </c>
       <c r="W24" t="n">
-        <v>0.2844930707910554</v>
+        <v>0.19983065970097</v>
       </c>
       <c r="X24" t="n">
-        <v>0.2774557643190154</v>
+        <v>0.1859759571284243</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.271824967808845</v>
+        <v>0.1741647325019855</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.2673894820374494</v>
+        <v>0.1640973522206186</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.263970615179774</v>
+        <v>0.1555154087754622</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.261417297784399</v>
+        <v>0.1481970652112233</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.2596018239868011</v>
+        <v>0.1419525752021242</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.2584161864173512</v>
+        <v>0.1366201144137832</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.2577689517259891</v>
+        <v>0.1320619909800818</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.2575826154151545</v>
+        <v>0.1281612587284694</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.2577913737724856</v>
+        <v>0.1248187289441724</v>
       </c>
       <c r="AH24" t="n">
         <v>14</v>
@@ -3267,100 +3267,100 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6.095968016201018</v>
+        <v>7.453806259768228</v>
       </c>
       <c r="C25" t="n">
-        <v>1.096063195603643</v>
+        <v>1.08040763995496</v>
       </c>
       <c r="D25" t="n">
-        <v>1.199497827787825</v>
+        <v>1.186118236968888</v>
       </c>
       <c r="E25" t="n">
-        <v>1.239843344590151</v>
+        <v>1.234576902701505</v>
       </c>
       <c r="F25" t="n">
-        <v>1.230463868671279</v>
+        <v>1.232939950107375</v>
       </c>
       <c r="G25" t="n">
-        <v>1.18781520601701</v>
+        <v>1.19503583029917</v>
       </c>
       <c r="H25" t="n">
-        <v>1.12486808244279</v>
+        <v>1.133378589982327</v>
       </c>
       <c r="I25" t="n">
-        <v>1.050962155377977</v>
+        <v>1.057749010429305</v>
       </c>
       <c r="J25" t="n">
-        <v>0.9725516020350676</v>
+        <v>0.9752984800016561</v>
       </c>
       <c r="K25" t="n">
-        <v>0.8939616170173234</v>
+        <v>0.8910366763950419</v>
       </c>
       <c r="L25" t="n">
-        <v>0.8179882680318196</v>
+        <v>0.8083380746932918</v>
       </c>
       <c r="M25" t="n">
-        <v>0.7463453768961077</v>
+        <v>0.7293700062864009</v>
       </c>
       <c r="N25" t="n">
-        <v>0.6799907899067706</v>
+        <v>0.6554288076417262</v>
       </c>
       <c r="O25" t="n">
-        <v>0.6193624948202048</v>
+        <v>0.5871948447026523</v>
       </c>
       <c r="P25" t="n">
-        <v>0.564548414815132</v>
+        <v>0.5249221964499957</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.5154076929565226</v>
+        <v>0.4685777879026611</v>
       </c>
       <c r="R25" t="n">
-        <v>0.4716566171896388</v>
+        <v>0.4179422300945003</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4329288565680295</v>
+        <v>0.3726820221271718</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3988171074296308</v>
+        <v>0.3324005321163804</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3689013509669344</v>
+        <v>0.2966733750976909</v>
       </c>
       <c r="V25" t="n">
-        <v>0.3427675253443612</v>
+        <v>0.2650724058872219</v>
       </c>
       <c r="W25" t="n">
-        <v>0.3200193860838115</v>
+        <v>0.237181473465546</v>
       </c>
       <c r="X25" t="n">
-        <v>0.3002855716327971</v>
+        <v>0.2126062716191277</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.2832233355571947</v>
+        <v>0.1909800093697326</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.2685199998249619</v>
+        <v>0.1719661667037058</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.2558928860396822</v>
+        <v>0.1552592592004603</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.2450882643112426</v>
+        <v>0.1405842808272264</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.2358797013586758</v>
+        <v>0.1276953056689048</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.2280660746874337</v>
+        <v>0.1163735902124238</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.2214694366852161</v>
+        <v>0.1064254155532159</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.2159328527188974</v>
+        <v>0.09767983415794025</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.2113182945318649</v>
+        <v>0.0899864315516804</v>
       </c>
       <c r="AH25" t="n">
         <v>14</v>
@@ -3382,100 +3382,100 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7643338639054155</v>
+        <v>0.568156486673322</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6794576445684123</v>
+        <v>0.7051078775072933</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4557895653793967</v>
+        <v>0.4655801354592282</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3920395414662212</v>
+        <v>0.3850411324493029</v>
       </c>
       <c r="F26" t="n">
-        <v>0.368812286855662</v>
+        <v>0.3558816316952129</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3560485864224566</v>
+        <v>0.3413545910789507</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3463984836868831</v>
+        <v>0.330586609967772</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3381235102104846</v>
+        <v>0.3207977825379112</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3307848861645487</v>
+        <v>0.3114510133706248</v>
       </c>
       <c r="K26" t="n">
-        <v>0.3242205519009964</v>
+        <v>0.3025337276699565</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3183206624896777</v>
+        <v>0.2941035539514416</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3129882616996887</v>
+        <v>0.2861917315865892</v>
       </c>
       <c r="N26" t="n">
-        <v>0.3081375887326635</v>
+        <v>0.2787972350077548</v>
       </c>
       <c r="O26" t="n">
-        <v>0.3036965282642691</v>
+        <v>0.271898017389445</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2996071836318829</v>
+        <v>0.265461496817814</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.2958246140753729</v>
+        <v>0.2594514302870629</v>
       </c>
       <c r="R26" t="n">
-        <v>0.29231466240477</v>
+        <v>0.2538317950143487</v>
       </c>
       <c r="S26" t="n">
-        <v>0.2890515876759171</v>
+        <v>0.248568722438469</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2860158975232122</v>
+        <v>0.2436312921638419</v>
       </c>
       <c r="U26" t="n">
-        <v>0.2831925450360872</v>
+        <v>0.2389917064722334</v>
       </c>
       <c r="V26" t="n">
-        <v>0.280569521836707</v>
+        <v>0.2346251549774743</v>
       </c>
       <c r="W26" t="n">
-        <v>0.2781368130223862</v>
+        <v>0.230509544037624</v>
       </c>
       <c r="X26" t="n">
-        <v>0.2758856537515805</v>
+        <v>0.2266251846795837</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.2738080228731639</v>
+        <v>0.2229544862603136</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.2718963148191211</v>
+        <v>0.2194816771996445</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.2701431406574594</v>
+        <v>0.216192560249275</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.2685412194469139</v>
+        <v>0.21307430271898</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.2670833303242614</v>
+        <v>0.2101152588197037</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.2657623035275986</v>
+        <v>0.2073048200523335</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.2645710347434914</v>
+        <v>0.2046332893801817</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.2635025119148925</v>
+        <v>0.2020917752238098</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.2625498471932538</v>
+        <v>0.199672101813066</v>
       </c>
       <c r="AH26" t="n">
         <v>14</v>
@@ -3497,100 +3497,100 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>23.85285233833792</v>
+        <v>27.89063927460766</v>
       </c>
       <c r="C27" t="n">
-        <v>1.675740776700782</v>
+        <v>2.008730807757649</v>
       </c>
       <c r="D27" t="n">
-        <v>1.728201198591835</v>
+        <v>2.151537377320219</v>
       </c>
       <c r="E27" t="n">
-        <v>1.617818726878664</v>
+        <v>2.102867866792064</v>
       </c>
       <c r="F27" t="n">
-        <v>1.440435616090725</v>
+        <v>1.949778063216193</v>
       </c>
       <c r="G27" t="n">
-        <v>1.246743595021312</v>
+        <v>1.748876090964233</v>
       </c>
       <c r="H27" t="n">
-        <v>1.062206660777301</v>
+        <v>1.534890260217662</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8982415537215107</v>
+        <v>1.327855294771562</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7585745306984183</v>
+        <v>1.138296325812027</v>
       </c>
       <c r="K27" t="n">
-        <v>0.642906444105198</v>
+        <v>0.9708018219330715</v>
       </c>
       <c r="L27" t="n">
-        <v>0.5490152323206412</v>
+        <v>0.8264049944659585</v>
       </c>
       <c r="M27" t="n">
-        <v>0.4739371514785333</v>
+        <v>0.7041305252663933</v>
       </c>
       <c r="N27" t="n">
-        <v>0.4146041141912544</v>
+        <v>0.6019744035471316</v>
       </c>
       <c r="O27" t="n">
-        <v>0.3681629845334989</v>
+        <v>0.5175067429180937</v>
       </c>
       <c r="P27" t="n">
-        <v>0.3321127122324157</v>
+        <v>0.4482282619884099</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.3043407907549635</v>
+        <v>0.3917687195656396</v>
       </c>
       <c r="R27" t="n">
-        <v>0.283107370602003</v>
+        <v>0.3459861195471989</v>
       </c>
       <c r="S27" t="n">
-        <v>0.2670051402003859</v>
+        <v>0.30900536079979</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2549108211177821</v>
+        <v>0.2792214133329365</v>
       </c>
       <c r="U27" t="n">
-        <v>0.2459367658817761</v>
+        <v>0.255283019081692</v>
       </c>
       <c r="V27" t="n">
-        <v>0.2393868111776467</v>
+        <v>0.2360669065751118</v>
       </c>
       <c r="W27" t="n">
-        <v>0.2347180544907498</v>
+        <v>0.2206485765025604</v>
       </c>
       <c r="X27" t="n">
-        <v>0.2315088584716815</v>
+        <v>0.20827317525981</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.2294326912271508</v>
+        <v>0.1983283598065207</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.2282371027731355</v>
+        <v>0.1903200541293612</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.2277270473117768</v>
+        <v>0.1838513930734073</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.2277517851473894</v>
+        <v>0.1786048014327171</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.228194676537436</v>
+        <v>0.1743269708427662</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.2289652781634577</v>
+        <v>0.1708164122501491</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.2299932525429573</v>
+        <v>0.167913237217185</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.2312236922930898</v>
+        <v>0.1654908311407024</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.2326135408247697</v>
+        <v>0.1634491092710419</v>
       </c>
       <c r="AH27" t="n">
         <v>11</v>
@@ -3612,100 +3612,100 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9.815125808284071</v>
+        <v>4.781603050592282</v>
       </c>
       <c r="C28" t="n">
-        <v>1.126490131965061</v>
+        <v>0.9722865337000783</v>
       </c>
       <c r="D28" t="n">
-        <v>1.093032764113632</v>
+        <v>0.8907222706030939</v>
       </c>
       <c r="E28" t="n">
-        <v>1.000725154996965</v>
+        <v>0.8175683817451415</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8881872419685722</v>
+        <v>0.7425824905984683</v>
       </c>
       <c r="G28" t="n">
-        <v>0.7758653830007809</v>
+        <v>0.6679191690666956</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6735608472831681</v>
+        <v>0.5974392205210088</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5851522840438207</v>
+        <v>0.5338810111019214</v>
       </c>
       <c r="J28" t="n">
-        <v>0.5113174345623265</v>
+        <v>0.4785240159481354</v>
       </c>
       <c r="K28" t="n">
-        <v>0.4511151952284951</v>
+        <v>0.4315508813563552</v>
       </c>
       <c r="L28" t="n">
-        <v>0.4028926997134891</v>
+        <v>0.3924740661249213</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3647902596759567</v>
+        <v>0.3604638976605506</v>
       </c>
       <c r="N28" t="n">
-        <v>0.3350074621872025</v>
+        <v>0.3345646738564544</v>
       </c>
       <c r="O28" t="n">
-        <v>0.3119293386433196</v>
+        <v>0.3138233825621791</v>
       </c>
       <c r="P28" t="n">
-        <v>0.294172744049311</v>
+        <v>0.2973587125805351</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.2805893119419572</v>
+        <v>0.2843922410351064</v>
       </c>
       <c r="R28" t="n">
-        <v>0.2702466543357167</v>
+        <v>0.2742570964212032</v>
       </c>
       <c r="S28" t="n">
-        <v>0.2624003971103784</v>
+        <v>0.2663941192621227</v>
       </c>
       <c r="T28" t="n">
-        <v>0.2564640775226716</v>
+        <v>0.26034179070867</v>
       </c>
       <c r="U28" t="n">
-        <v>0.2519805723076162</v>
+        <v>0.2557236883777503</v>
       </c>
       <c r="V28" t="n">
-        <v>0.2485967446608208</v>
+        <v>0.2522356118560275</v>
       </c>
       <c r="W28" t="n">
-        <v>0.2460418709718586</v>
+        <v>0.2496335113125979</v>
       </c>
       <c r="X28" t="n">
-        <v>0.2441098005937634</v>
+        <v>0.247722742601023</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.24264450451632</v>
+        <v>0.2463488172571371</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.2415285508679187</v>
+        <v>0.2453896202251813</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.2406740264041685</v>
+        <v>0.2447489697671777</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.240015455172866</v>
+        <v>0.2443513531428015</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.2395043200047258</v>
+        <v>0.2441376634166471</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.2391048533702873</v>
+        <v>0.2440617718707154</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.2387908229835058</v>
+        <v>0.2440877878024332</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.2385430902960996</v>
+        <v>0.2441878776496602</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.2383477652433041</v>
+        <v>0.2443405354621132</v>
       </c>
       <c r="AH28" t="n">
         <v>14</v>
@@ -3727,100 +3727,100 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.111568890108937</v>
+        <v>1.597618990407933</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4574163787715343</v>
+        <v>0.4286955335667225</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4837487508359488</v>
+        <v>0.4667643587875417</v>
       </c>
       <c r="E29" t="n">
-        <v>0.5091862859816533</v>
+        <v>0.4841618432541296</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5220526619848932</v>
+        <v>0.4849459377014233</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5230662871321541</v>
+        <v>0.4740551399613637</v>
       </c>
       <c r="H29" t="n">
-        <v>0.515037827884436</v>
+        <v>0.4555125792134551</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5007352794360299</v>
+        <v>0.4323430279346936</v>
       </c>
       <c r="J29" t="n">
-        <v>0.4824175267001622</v>
+        <v>0.4067307523206693</v>
       </c>
       <c r="K29" t="n">
-        <v>0.4618098178419669</v>
+        <v>0.380208537438549</v>
       </c>
       <c r="L29" t="n">
-        <v>0.4401837213413748</v>
+        <v>0.3538216463146636</v>
       </c>
       <c r="M29" t="n">
-        <v>0.4184505354374495</v>
+        <v>0.3282578394724784</v>
       </c>
       <c r="N29" t="n">
-        <v>0.3972442808270744</v>
+        <v>0.3039467751226504</v>
       </c>
       <c r="O29" t="n">
-        <v>0.37698954786943</v>
+        <v>0.2811345439372304</v>
       </c>
       <c r="P29" t="n">
-        <v>0.3579550090531801</v>
+        <v>0.2599388477149631</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.3402948278736117</v>
+        <v>0.240389432290229</v>
       </c>
       <c r="R29" t="n">
-        <v>0.3240803163841666</v>
+        <v>0.2224574343568707</v>
       </c>
       <c r="S29" t="n">
-        <v>0.3093239201710624</v>
+        <v>0.2060764717079715</v>
       </c>
       <c r="T29" t="n">
-        <v>0.2959972483327741</v>
+        <v>0.191157630885354</v>
       </c>
       <c r="U29" t="n">
-        <v>0.2840445221502323</v>
+        <v>0.1775999750896781</v>
       </c>
       <c r="V29" t="n">
-        <v>0.2733925214894804</v>
+        <v>0.1652977856900939</v>
       </c>
       <c r="W29" t="n">
-        <v>0.2639578673991149</v>
+        <v>0.154145438906584</v>
       </c>
       <c r="X29" t="n">
-        <v>0.2556522879096393</v>
+        <v>0.144040583988622</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.2483863639367792</v>
+        <v>0.1348861128853945</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.2420721355727544</v>
+        <v>0.1265912799419637</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.2366248589665944</v>
+        <v>0.1190722325857998</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.2319641346672008</v>
+        <v>0.1122521418416802</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.2280145750820693</v>
+        <v>0.1060610683961932</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.224706137922</v>
+        <v>0.1004356609629731</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.221974221296409</v>
+        <v>0.09531875522174944</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.2197595922787142</v>
+        <v>0.09065892088423455</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.2180082025672747</v>
+        <v>0.08640998943976506</v>
       </c>
       <c r="AH29" t="n">
         <v>18</v>
@@ -3842,100 +3842,100 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3.616419079665482</v>
+        <v>2.271518551224928</v>
       </c>
       <c r="C30" t="n">
-        <v>1.373350042284936</v>
+        <v>1.382564182462109</v>
       </c>
       <c r="D30" t="n">
-        <v>1.00103773901794</v>
+        <v>0.8836497442005129</v>
       </c>
       <c r="E30" t="n">
-        <v>0.8988403489093139</v>
+        <v>0.712240662270056</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8708180585167048</v>
+        <v>0.6604011743463154</v>
       </c>
       <c r="G30" t="n">
-        <v>0.8577361879984337</v>
+        <v>0.6443065731145319</v>
       </c>
       <c r="H30" t="n">
-        <v>0.8440536382265676</v>
+        <v>0.6351211600622182</v>
       </c>
       <c r="I30" t="n">
-        <v>0.8266319768481044</v>
+        <v>0.6241653084899838</v>
       </c>
       <c r="J30" t="n">
-        <v>0.8055461476513058</v>
+        <v>0.6095310054464358</v>
       </c>
       <c r="K30" t="n">
-        <v>0.7815678135026737</v>
+        <v>0.591423591241516</v>
       </c>
       <c r="L30" t="n">
-        <v>0.7555105894878383</v>
+        <v>0.5706066331124662</v>
       </c>
       <c r="M30" t="n">
-        <v>0.7280800871253557</v>
+        <v>0.5479002795151358</v>
       </c>
       <c r="N30" t="n">
-        <v>0.699856347655782</v>
+        <v>0.5240311490778585</v>
       </c>
       <c r="O30" t="n">
-        <v>0.6713075207954704</v>
+        <v>0.4995985447630857</v>
       </c>
       <c r="P30" t="n">
-        <v>0.6428080241554611</v>
+        <v>0.4750783711104309</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.6146547927671118</v>
+        <v>0.4508382354499735</v>
       </c>
       <c r="R30" t="n">
-        <v>0.5870806754852315</v>
+        <v>0.4271546753348841</v>
       </c>
       <c r="S30" t="n">
-        <v>0.5602653369727733</v>
+        <v>0.4042294301655178</v>
       </c>
       <c r="T30" t="n">
-        <v>0.5343442032306168</v>
+        <v>0.3822037902696889</v>
       </c>
       <c r="U30" t="n">
-        <v>0.5094159000976652</v>
+        <v>0.3611708359265413</v>
       </c>
       <c r="V30" t="n">
-        <v>0.4855485132558587</v>
+        <v>0.3411856729542881</v>
       </c>
       <c r="W30" t="n">
-        <v>0.4627849013241793</v>
+        <v>0.3222738776809767</v>
       </c>
       <c r="X30" t="n">
-        <v>0.4411472264727531</v>
+        <v>0.3044383923078111</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.4206408232774312</v>
+        <v>0.2876651059300514</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.4012574987609629</v>
+        <v>0.2719273361637685</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.3829783388248117</v>
+        <v>0.2571894006448706</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.3657760845280332</v>
+        <v>0.2434094411949899</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.3496171333651261</v>
+        <v>0.230541638443471</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.3344632143160707</v>
+        <v>0.2185379321770419</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.3202727801377104</v>
+        <v>0.2073493430057147</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.3070021556896587</v>
+        <v>0.1969269740687421</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.2946064768257464</v>
+        <v>0.1872227572570189</v>
       </c>
       <c r="AH30" t="n">
         <v>17</v>
@@ -3957,100 +3957,100 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.006163483507753</v>
+        <v>0.800075876957103</v>
       </c>
       <c r="C31" t="n">
-        <v>0.4471042693544809</v>
+        <v>0.4714938318223333</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4382375656886543</v>
+        <v>0.4139371915967877</v>
       </c>
       <c r="E31" t="n">
-        <v>0.4288071460253402</v>
+        <v>0.397170148326533</v>
       </c>
       <c r="F31" t="n">
-        <v>0.4176833784425397</v>
+        <v>0.3866257608736139</v>
       </c>
       <c r="G31" t="n">
-        <v>0.4058657047131675</v>
+        <v>0.3749431842243395</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3942191869459971</v>
+        <v>0.3614344580031922</v>
       </c>
       <c r="I31" t="n">
-        <v>0.3833101681101117</v>
+        <v>0.3468807676598253</v>
       </c>
       <c r="J31" t="n">
-        <v>0.3734296176974694</v>
+        <v>0.3321206825939674</v>
       </c>
       <c r="K31" t="n">
-        <v>0.364674224480326</v>
+        <v>0.3177530518166951</v>
       </c>
       <c r="L31" t="n">
-        <v>0.3570237000773169</v>
+        <v>0.3041376531500234</v>
       </c>
       <c r="M31" t="n">
-        <v>0.3503974759745769</v>
+        <v>0.2914574860781523</v>
       </c>
       <c r="N31" t="n">
-        <v>0.3446909794984431</v>
+        <v>0.2797790346400046</v>
       </c>
       <c r="O31" t="n">
-        <v>0.3397964795170731</v>
+        <v>0.2690973743054101</v>
       </c>
       <c r="P31" t="n">
-        <v>0.3356136866220102</v>
+        <v>0.2593668331398731</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.3320541308840491</v>
+        <v>0.2505207775463581</v>
       </c>
       <c r="R31" t="n">
-        <v>0.3290420627784661</v>
+        <v>0.2424839021164347</v>
       </c>
       <c r="S31" t="n">
-        <v>0.3265136058087787</v>
+        <v>0.2351795768222228</v>
       </c>
       <c r="T31" t="n">
-        <v>0.3244151794549991</v>
+        <v>0.2285340241302101</v>
       </c>
       <c r="U31" t="n">
-        <v>0.3227017522428927</v>
+        <v>0.2224785072381947</v>
       </c>
       <c r="V31" t="n">
-        <v>0.3213352046631265</v>
+        <v>0.216950298367942</v>
       </c>
       <c r="W31" t="n">
-        <v>0.3202829195570567</v>
+        <v>0.2118929198071615</v>
       </c>
       <c r="X31" t="n">
-        <v>0.3195166293226961</v>
+        <v>0.2072559692320104</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.3190115052678959</v>
+        <v>0.2029947235697016</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.3187454557439306</v>
+        <v>0.1990696404434814</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.3186985947277099</v>
+        <v>0.1954458283835583</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.318852844415335</v>
+        <v>0.1920925267988925</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.3191916402343644</v>
+        <v>0.1889826178696215</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.3196997123616356</v>
+        <v>0.1860921809458871</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.3203629232865839</v>
+        <v>0.1834000930843265</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.3211681457233563</v>
+        <v>0.1808876753177349</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.3221031691089178</v>
+        <v>0.1785383820439866</v>
       </c>
       <c r="AH31" t="n">
         <v>17</v>
@@ -4072,100 +4072,100 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.790913864889146</v>
+        <v>2.593939588919881</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7289170746783225</v>
+        <v>0.7103112628839456</v>
       </c>
       <c r="D32" t="n">
-        <v>0.7310151799140151</v>
+        <v>0.7080560056701481</v>
       </c>
       <c r="E32" t="n">
-        <v>0.7098579569842139</v>
+        <v>0.6946582713437646</v>
       </c>
       <c r="F32" t="n">
-        <v>0.6736738434214131</v>
+        <v>0.6678717695468184</v>
       </c>
       <c r="G32" t="n">
-        <v>0.6309558827920471</v>
+        <v>0.6329541971678497</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5871482697271951</v>
+        <v>0.5946870856605019</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5453782359196033</v>
+        <v>0.5564096614888709</v>
       </c>
       <c r="J32" t="n">
-        <v>0.5072473973249444</v>
+        <v>0.5201723513445342</v>
       </c>
       <c r="K32" t="n">
-        <v>0.4734118865753042</v>
+        <v>0.4870855565374169</v>
       </c>
       <c r="L32" t="n">
-        <v>0.4439682651730064</v>
+        <v>0.4576298256168719</v>
       </c>
       <c r="M32" t="n">
-        <v>0.4187013840058841</v>
+        <v>0.4318878096792142</v>
       </c>
       <c r="N32" t="n">
-        <v>0.3972398130215869</v>
+        <v>0.4097060116540597</v>
       </c>
       <c r="O32" t="n">
-        <v>0.3791506291322699</v>
+        <v>0.3908029713122256</v>
       </c>
       <c r="P32" t="n">
-        <v>0.3639949598916373</v>
+        <v>0.374839156784834</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.351358528017426</v>
+        <v>0.3614604450998175</v>
       </c>
       <c r="R32" t="n">
-        <v>0.3408666039942451</v>
+        <v>0.3503238509855367</v>
       </c>
       <c r="S32" t="n">
-        <v>0.3321895170553232</v>
+        <v>0.3411115996518873</v>
       </c>
       <c r="T32" t="n">
-        <v>0.325042692289185</v>
+        <v>0.3335377384015671</v>
       </c>
       <c r="U32" t="n">
-        <v>0.31918372920164</v>
+        <v>0.3273501221583706</v>
       </c>
       <c r="V32" t="n">
-        <v>0.3144080796772422</v>
+        <v>0.3223296566532824</v>
       </c>
       <c r="W32" t="n">
-        <v>0.3105442597642451</v>
+        <v>0.3182880280684343</v>
       </c>
       <c r="X32" t="n">
-        <v>0.307449129666766</v>
+        <v>0.3150647031495198</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.3050035244892609</v>
+        <v>0.312523685648042</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.303108363643013</v>
+        <v>0.3105503178722187</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.3016812751170445</v>
+        <v>0.3090482879543809</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.300653719207678</v>
+        <v>0.3079369217732733</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.2999685697388313</v>
+        <v>0.3071487878374284</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.2995780994761366</v>
+        <v>0.3066276132625985</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.2994423140305691</v>
+        <v>0.306326492087199</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.2995275810679924</v>
+        <v>0.3062063587410869</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.2998055066158629</v>
+        <v>0.3062346963033689</v>
       </c>
       <c r="AH32" t="n">
         <v>20</v>
@@ -4187,100 +4187,100 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>6.239617236873682</v>
+        <v>4.906260416107228</v>
       </c>
       <c r="C33" t="n">
-        <v>1.088053498219465</v>
+        <v>1.10921839902341</v>
       </c>
       <c r="D33" t="n">
-        <v>1.076880727022737</v>
+        <v>0.9849314324254226</v>
       </c>
       <c r="E33" t="n">
-        <v>1.109767063897813</v>
+        <v>0.9939490334828091</v>
       </c>
       <c r="F33" t="n">
-        <v>1.125560924351578</v>
+        <v>0.9921028183643281</v>
       </c>
       <c r="G33" t="n">
-        <v>1.118952521782157</v>
+        <v>0.971118015279135</v>
       </c>
       <c r="H33" t="n">
-        <v>1.094198923432407</v>
+        <v>0.9352152437597417</v>
       </c>
       <c r="I33" t="n">
-        <v>1.056422080853524</v>
+        <v>0.8893497459263933</v>
       </c>
       <c r="J33" t="n">
-        <v>1.009960177232967</v>
+        <v>0.8374917675847615</v>
       </c>
       <c r="K33" t="n">
-        <v>0.9582186392922087</v>
+        <v>0.7826072411296313</v>
       </c>
       <c r="L33" t="n">
-        <v>0.9037953711636446</v>
+        <v>0.7268570844172221</v>
       </c>
       <c r="M33" t="n">
-        <v>0.8486325431057629</v>
+        <v>0.6717829135170648</v>
       </c>
       <c r="N33" t="n">
-        <v>0.7941503900496693</v>
+        <v>0.6184544304028123</v>
       </c>
       <c r="O33" t="n">
-        <v>0.7413583811758503</v>
+        <v>0.5675838530432662</v>
       </c>
       <c r="P33" t="n">
-        <v>0.6909460692047951</v>
+        <v>0.5196147034692127</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.6433566621043716</v>
+        <v>0.474790712950923</v>
       </c>
       <c r="R33" t="n">
-        <v>0.5988461052107856</v>
+        <v>0.4332091782725444</v>
       </c>
       <c r="S33" t="n">
-        <v>0.5575301200658314</v>
+        <v>0.3948620936392586</v>
       </c>
       <c r="T33" t="n">
-        <v>0.5194213272451359</v>
+        <v>0.3596676620458366</v>
       </c>
       <c r="U33" t="n">
-        <v>0.4844582835075498</v>
+        <v>0.3274942498306186</v>
       </c>
       <c r="V33" t="n">
-        <v>0.4525279867527839</v>
+        <v>0.2981784271789923</v>
       </c>
       <c r="W33" t="n">
-        <v>0.4234831488750831</v>
+        <v>0.2715384019455256</v>
       </c>
       <c r="X33" t="n">
-        <v>0.3971553106059547</v>
+        <v>0.2473838845079291</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.373364675898835</v>
+        <v>0.2255232042183496</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.3519273761175813</v>
+        <v>0.2057683235281768</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.3326607343514075</v>
+        <v>0.1879382561802895</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.3153869847229089</v>
+        <v>0.1718612845291565</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.2999358073306029</v>
+        <v>0.1573762827027788</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.2861459632295176</v>
+        <v>0.1443333825164034</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.2738662525949092</v>
+        <v>0.1325941641232472</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.2629559702706409</v>
+        <v>0.1220315103445011</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.2532849939861954</v>
+        <v>0.1125292300236261</v>
       </c>
       <c r="AH33" t="n">
         <v>18</v>
@@ -4302,100 +4302,100 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4.517216798145682</v>
+        <v>3.773704551867908</v>
       </c>
       <c r="C34" t="n">
-        <v>0.9838898524064077</v>
+        <v>1.060437580602296</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9610799394642662</v>
+        <v>0.9314557237653242</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9178699543419017</v>
+        <v>0.8698906042852443</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8572773865448199</v>
+        <v>0.8067988053993836</v>
       </c>
       <c r="G34" t="n">
-        <v>0.7888289173968941</v>
+        <v>0.7395887294170745</v>
       </c>
       <c r="H34" t="n">
-        <v>0.7194786458293504</v>
+        <v>0.6721656833450269</v>
       </c>
       <c r="I34" t="n">
-        <v>0.6534960893263577</v>
+        <v>0.607887221030846</v>
       </c>
       <c r="J34" t="n">
-        <v>0.5931869852527619</v>
+        <v>0.5487531762460475</v>
       </c>
       <c r="K34" t="n">
-        <v>0.539563536725413</v>
+        <v>0.4956921598475756</v>
       </c>
       <c r="L34" t="n">
-        <v>0.4928324954258863</v>
+        <v>0.448926497600903</v>
       </c>
       <c r="M34" t="n">
-        <v>0.4527266140546879</v>
+        <v>0.4082512559002038</v>
       </c>
       <c r="N34" t="n">
-        <v>0.4187224156252204</v>
+        <v>0.3732247882827161</v>
       </c>
       <c r="O34" t="n">
-        <v>0.3901794526416212</v>
+        <v>0.3432927009205687</v>
       </c>
       <c r="P34" t="n">
-        <v>0.3664265307156291</v>
+        <v>0.3178655763779085</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.3468126756335584</v>
+        <v>0.29636560814271</v>
       </c>
       <c r="R34" t="n">
-        <v>0.330735058244442</v>
+        <v>0.2782527661715135</v>
       </c>
       <c r="S34" t="n">
-        <v>0.3176521801360331</v>
+        <v>0.2630377632235932</v>
       </c>
       <c r="T34" t="n">
-        <v>0.307087905227782</v>
+        <v>0.2502867317410841</v>
       </c>
       <c r="U34" t="n">
-        <v>0.2986300478138626</v>
+        <v>0.2396208880140271</v>
       </c>
       <c r="V34" t="n">
-        <v>0.2919259437857749</v>
+        <v>0.2307133406308513</v>
       </c>
       <c r="W34" t="n">
-        <v>0.2866765597263834</v>
+        <v>0.2232844380343993</v>
       </c>
       <c r="X34" t="n">
-        <v>0.2826301080516956</v>
+        <v>0.2170965354027544</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.2795757466782646</v>
+        <v>0.2119487171258213</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.2773376867225115</v>
+        <v>0.207671784235831</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.2757698682316652</v>
+        <v>0.2041236689962339</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.2747512619240126</v>
+        <v>0.2011853456226857</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.2741817937314446</v>
+        <v>0.198757248969102</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.2739788544712891</v>
+        <v>0.1967561797176155</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.274074339652169</v>
+        <v>0.1951126568134405</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.2744121578092706</v>
+        <v>0.1937686699353096</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.2749461455991941</v>
+        <v>0.1926757829061322</v>
       </c>
       <c r="AH34" t="n">
         <v>18</v>
@@ -4417,100 +4417,100 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>9.305344946643528</v>
+        <v>5.233685772203451</v>
       </c>
       <c r="C35" t="n">
-        <v>1.062818597783973</v>
+        <v>0.8395003639198599</v>
       </c>
       <c r="D35" t="n">
-        <v>1.22297737111922</v>
+        <v>0.9538284018909526</v>
       </c>
       <c r="E35" t="n">
-        <v>1.315518497078834</v>
+        <v>1.015037682816523</v>
       </c>
       <c r="F35" t="n">
-        <v>1.349256470078204</v>
+        <v>1.03164424663961</v>
       </c>
       <c r="G35" t="n">
-        <v>1.341091447171818</v>
+        <v>1.017909762649115</v>
       </c>
       <c r="H35" t="n">
-        <v>1.304728095815403</v>
+        <v>0.9843644814323351</v>
       </c>
       <c r="I35" t="n">
-        <v>1.250268285104519</v>
+        <v>0.9383927701734167</v>
       </c>
       <c r="J35" t="n">
-        <v>1.184970156039782</v>
+        <v>0.8851516629417917</v>
       </c>
       <c r="K35" t="n">
-        <v>1.113998162231585</v>
+        <v>0.8282513454267659</v>
       </c>
       <c r="L35" t="n">
-        <v>1.040993653890174</v>
+        <v>0.7702139272118016</v>
       </c>
       <c r="M35" t="n">
-        <v>0.96848822720052</v>
+        <v>0.7127838445790186</v>
       </c>
       <c r="N35" t="n">
-        <v>0.898202287041742</v>
+        <v>0.6571430077258695</v>
       </c>
       <c r="O35" t="n">
-        <v>0.8312625119950329</v>
+        <v>0.6040636874528997</v>
       </c>
       <c r="P35" t="n">
-        <v>0.7683617998106971</v>
+        <v>0.5540193966232587</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.7098778575776824</v>
+        <v>0.5072665164198289</v>
       </c>
       <c r="R35" t="n">
-        <v>0.6559616164950273</v>
+        <v>0.4639049824134477</v>
       </c>
       <c r="S35" t="n">
-        <v>0.6066033406744372</v>
+        <v>0.4239236531744789</v>
       </c>
       <c r="T35" t="n">
-        <v>0.5616820744994174</v>
+        <v>0.3872342908545315</v>
       </c>
       <c r="U35" t="n">
-        <v>0.521002547630483</v>
+        <v>0.3536969773910974</v>
       </c>
       <c r="V35" t="n">
-        <v>0.4843225879288658</v>
+        <v>0.3231390412469791</v>
       </c>
       <c r="W35" t="n">
-        <v>0.4513733280612499</v>
+        <v>0.2953690457406717</v>
       </c>
       <c r="X35" t="n">
-        <v>0.4218739345648856</v>
+        <v>0.2701870130950532</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.3955421759596462</v>
+        <v>0.2473917808446178</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.3721018374851495</v>
+        <v>0.2267861792682529</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.3512877559702667</v>
+        <v>0.208180560522545</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.3328490695914954</v>
+        <v>0.1913950889480904</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.3165511399295718</v>
+        <v>0.1762611084100556</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.302176497727955</v>
+        <v>0.1626218299159869</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.2895250816932162</v>
+        <v>0.1503325262799907</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.2784139760358424</v>
+        <v>0.1392603766395143</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.2686768030618607</v>
+        <v>0.1292840694142527</v>
       </c>
       <c r="AH35" t="n">
         <v>16</v>
@@ -4532,100 +4532,100 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>6.382785636102462</v>
+        <v>5.346332896288602</v>
       </c>
       <c r="C36" t="n">
-        <v>0.913027398483758</v>
+        <v>0.8782174202848523</v>
       </c>
       <c r="D36" t="n">
-        <v>1.021395899748789</v>
+        <v>0.9499753237822438</v>
       </c>
       <c r="E36" t="n">
-        <v>1.074988371988296</v>
+        <v>0.9832701044018063</v>
       </c>
       <c r="F36" t="n">
-        <v>1.085698282538478</v>
+        <v>0.980165811475133</v>
       </c>
       <c r="G36" t="n">
-        <v>1.066706856784872</v>
+        <v>0.951411275666347</v>
       </c>
       <c r="H36" t="n">
-        <v>1.028293986473047</v>
+        <v>0.9062133962599127</v>
       </c>
       <c r="I36" t="n">
-        <v>0.9780548653140745</v>
+        <v>0.8514407512649901</v>
       </c>
       <c r="J36" t="n">
-        <v>0.9214624247761336</v>
+        <v>0.791979164648387</v>
       </c>
       <c r="K36" t="n">
-        <v>0.8623818812932573</v>
+        <v>0.7312098039905599</v>
       </c>
       <c r="L36" t="n">
-        <v>0.8034790572195365</v>
+        <v>0.6714086230727877</v>
       </c>
       <c r="M36" t="n">
-        <v>0.7465336170728215</v>
+        <v>0.6140508041053657</v>
       </c>
       <c r="N36" t="n">
-        <v>0.6926768268568787</v>
+        <v>0.5600371180110484</v>
       </c>
       <c r="O36" t="n">
-        <v>0.6425710000875566</v>
+        <v>0.5098609293895928</v>
       </c>
       <c r="P36" t="n">
-        <v>0.5965442262425448</v>
+        <v>0.4637309443710413</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.5546909278350405</v>
+        <v>0.4216610841057122</v>
       </c>
       <c r="R36" t="n">
-        <v>0.5169463886912691</v>
+        <v>0.3835359421064869</v>
       </c>
       <c r="S36" t="n">
-        <v>0.4831415283325116</v>
+        <v>0.3491581092780668</v>
       </c>
       <c r="T36" t="n">
-        <v>0.4530427482042972</v>
+        <v>0.31828204904867</v>
       </c>
       <c r="U36" t="n">
-        <v>0.426380551339796</v>
+        <v>0.2906380211845432</v>
       </c>
       <c r="V36" t="n">
-        <v>0.402869766025915</v>
+        <v>0.2659486721832368</v>
       </c>
       <c r="W36" t="n">
-        <v>0.3822235305564736</v>
+        <v>0.2439402513577844</v>
       </c>
       <c r="X36" t="n">
-        <v>0.3641626767714273</v>
+        <v>0.2243499170352327</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.3484217506939886</v>
+        <v>0.2069302250186008</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.3347526023952753</v>
+        <v>0.1914516110978877</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.3229262432214506</v>
+        <v>0.1777034683347224</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.3127334902707944</v>
+        <v>0.1654942611680822</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.3039847826886234</v>
+        <v>0.1546509993494003</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.2965094519927775</v>
+        <v>0.1450183056704187</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.2901546515306782</v>
+        <v>0.1364572450808653</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.2847840923347583</v>
+        <v>0.1288440335495636</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.280276689488467</v>
+        <v>0.1220687086813652</v>
       </c>
       <c r="AH36" t="n">
         <v>11</v>
